--- a/Testing.xlsx
+++ b/Testing.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -87,16 +87,6 @@
   </si>
   <si>
     <t>CountryCode</t>
-  </si>
-  <si>
-    <t>&lt;soap:Envelope xmlns:soap="http://www.w3.org/2003/05/soap-envelope" xmlns:web="http://www.oorsprong.org/websamples.countryinfo"&gt;
-   &lt;soap:Header/&gt;
-   &lt;soap:Body&gt;
-      &lt;web:CountryISOCode&gt;
-         &lt;web:sCountryName&gt;.&lt;/web:sCountryName&gt;
-      &lt;/web:CountryISOCode&gt;
-   &lt;/soap:Body&gt;
-&lt;/soap:Envelope&gt;</t>
   </si>
   <si>
     <t>A1</t>
@@ -235,12 +225,21 @@
   <si>
     <t>ERROR in  calculation</t>
   </si>
+  <si>
+    <t>&lt;soap:Envelope xmlns:soap="http://www.w3.org/2003/05/soap-envelope" xmlns:web="http://www.oorsprong.org/websamples.countryinfo"&gt;
+   &lt;soap:Header/&gt;
+   &lt;soap:Body&gt;
+       &lt;web:CapitalCity&gt;
+         &lt;web:sCountryISOCode&gt;?&lt;/web:sCountryISOCode&gt;
+       &lt;/web:CapitalCity&gt;
+   &lt;/soap:Body&gt;
+&lt;/soap:Envelope&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -590,21 +589,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="24.85546875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="32.140625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="18.85546875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="21.5703125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" width="19.42578125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" width="15.85546875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" width="21.7109375" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" width="21.140625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" width="39.28515625" collapsed="true"/>
+    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="24.81640625" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="32.1796875" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="18.81640625" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="21.54296875" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="15.81640625" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="21.7265625" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="21.1796875" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="39.26953125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -618,10 +617,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
         <v>29</v>
-      </c>
-      <c r="F1" t="s">
-        <v>30</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -636,9 +635,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>8</v>
@@ -647,30 +646,30 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -694,15 +693,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="17.28515625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="21.42578125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="25.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="90.5703125" collapsed="true"/>
+    <col min="1" max="1" width="17.26953125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="21.453125" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="25" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="90.54296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -716,9 +715,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="406" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>8</v>
@@ -727,32 +726,32 @@
         <v>14</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="11"/>
       <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -761,7 +760,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Testing.xlsx
+++ b/Testing.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>Ref\Id</t>
   </si>
@@ -240,6 +240,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -591,16 +592,16 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="24.81640625" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="32.1796875" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="18.81640625" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="21.54296875" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="19.453125" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.81640625" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="21.7265625" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="21.1796875" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="39.26953125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="24.81640625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="32.1796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="18.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="21.54296875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="19.453125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="15.81640625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" width="21.7265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" width="21.1796875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" width="39.26953125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -695,10 +696,10 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="21.453125" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="25" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="90.54296875" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="17.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="21.453125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="25.0" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="90.54296875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.35">
